--- a/data/fee due.xlsx
+++ b/data/fee due.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user1\Documents\branch_dashboard_redesigned\branch_dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1457DD60-45FF-413B-B82B-7F8830157EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DAD1D9-A6FB-4D13-AB84-61D208FA3682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{71D70DC9-DBAF-439E-8B35-4E3944DEB052}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="67">
   <si>
     <t>AGM Name</t>
   </si>
@@ -83,235 +83,163 @@
     <t>CY_FN_BN</t>
   </si>
   <si>
-    <t>Mr.M.V.Suresh</t>
-  </si>
-  <si>
-    <t>Mr.P Gopi Nath</t>
-  </si>
-  <si>
-    <t>Kakinada</t>
-  </si>
-  <si>
-    <t>KAKINADA 1</t>
-  </si>
-  <si>
     <t>DS</t>
   </si>
   <si>
-    <t>KAKINADA 2</t>
-  </si>
-  <si>
     <t>DS/RES</t>
   </si>
   <si>
-    <t>Kakinada 3</t>
-  </si>
-  <si>
-    <t>Kakinada 4</t>
-  </si>
-  <si>
-    <t>Kakinada 6</t>
-  </si>
-  <si>
-    <t>KAKINADA 7</t>
-  </si>
-  <si>
-    <t>Payakaraopeta</t>
-  </si>
-  <si>
-    <t>Sunkarapalem</t>
-  </si>
-  <si>
-    <t>Yanam</t>
-  </si>
-  <si>
-    <t>Mr M.V.L.Naresh</t>
-  </si>
-  <si>
-    <t>Rajahmundry - East</t>
-  </si>
-  <si>
-    <t>ANAPARTHI</t>
-  </si>
-  <si>
-    <t>DRAKSHARAMAM</t>
-  </si>
-  <si>
-    <t>MANDAPETA 2</t>
-  </si>
-  <si>
-    <t>RAMACHANDRAPURAM</t>
-  </si>
-  <si>
-    <t>RAVULAPALEM</t>
-  </si>
-  <si>
-    <t>Mr.P.Srinivas Rao</t>
-  </si>
-  <si>
-    <t>AMALAPURAM</t>
-  </si>
-  <si>
-    <t>AMALAPURAM 2</t>
-  </si>
-  <si>
-    <t>JAGGAMPETA</t>
-  </si>
-  <si>
-    <t>Pitapuram</t>
-  </si>
-  <si>
-    <t>Tuni 1</t>
-  </si>
-  <si>
-    <t>Tuni 2</t>
-  </si>
-  <si>
-    <t>YELESWARAM</t>
-  </si>
-  <si>
-    <t>Mr.Uday Shankar V</t>
-  </si>
-  <si>
-    <t>KOVVUR</t>
-  </si>
-  <si>
-    <t>RAJAHMUNDRY 1</t>
-  </si>
-  <si>
-    <t>RAJAHMUNDRY 2</t>
-  </si>
-  <si>
-    <t>RAJAHMUNDRY 5</t>
-  </si>
-  <si>
-    <t>RAJAHMUNDRY 6</t>
-  </si>
-  <si>
-    <t>RAJAHMUNDRY 7</t>
-  </si>
-  <si>
-    <t>RAJAHMUNDRY BOMMURU</t>
-  </si>
-  <si>
-    <t>KOTHAPETA</t>
-  </si>
-  <si>
-    <t>Mr.PSSSV Prasad</t>
-  </si>
-  <si>
-    <t>Visakhapatnam</t>
-  </si>
-  <si>
-    <t>KOMMADI</t>
-  </si>
-  <si>
-    <t>MADHURAWADA</t>
-  </si>
-  <si>
     <t>RES/SEMI</t>
   </si>
   <si>
-    <t>Mr.Ahmedali</t>
-  </si>
-  <si>
-    <t>ASILMETTA</t>
-  </si>
-  <si>
     <t>RES</t>
   </si>
   <si>
-    <t>ASILMETTA 3</t>
-  </si>
-  <si>
-    <t>Dwarakanagar IPL</t>
-  </si>
-  <si>
     <t>DS/RES/SEMI</t>
   </si>
   <si>
-    <t>MADHURAWADA 2</t>
-  </si>
-  <si>
-    <t>MVP COLONY</t>
-  </si>
-  <si>
-    <t>NAD</t>
-  </si>
-  <si>
-    <t>NAD 2</t>
-  </si>
-  <si>
-    <t>PENDURTY</t>
-  </si>
-  <si>
-    <t>Mr.M.Ramana</t>
-  </si>
-  <si>
-    <t>ANAKAPALLI</t>
-  </si>
-  <si>
-    <t>GAJUWAKA</t>
-  </si>
-  <si>
-    <t>GAJUWAKA 2</t>
-  </si>
-  <si>
-    <t>KURMANNAPALEM</t>
-  </si>
-  <si>
-    <t>NARSIPATNAM</t>
-  </si>
-  <si>
-    <t>YALAMANCHILI</t>
-  </si>
-  <si>
-    <t>Mr.S.Raminaidu</t>
-  </si>
-  <si>
-    <t>PALASA</t>
-  </si>
-  <si>
-    <t>SRIKAKULAM</t>
-  </si>
-  <si>
-    <t>SRIKAKULAM 2</t>
-  </si>
-  <si>
-    <t>Mr.V. Srinivasa Rao</t>
-  </si>
-  <si>
-    <t>BOBBILI</t>
-  </si>
-  <si>
-    <t>BOBBILI 2</t>
-  </si>
-  <si>
-    <t>PARVATHIPURAM</t>
-  </si>
-  <si>
-    <t>RAJAM</t>
-  </si>
-  <si>
-    <t>VIZIANAGARAM</t>
-  </si>
-  <si>
-    <t>VIZIANAGARAM 2</t>
-  </si>
-  <si>
-    <t>MADHURAWADA 5</t>
-  </si>
-  <si>
-    <t>CHEEPURUPALLI</t>
-  </si>
-  <si>
-    <t>VIZIANAGARAM 3</t>
-  </si>
-  <si>
-    <t>MADHURAWADA 4</t>
-  </si>
-  <si>
-    <t>SRIKAKULAM 3</t>
+    <t>Kompally</t>
+  </si>
+  <si>
+    <t>HMT Colony</t>
+  </si>
+  <si>
+    <t>Kompally 2</t>
+  </si>
+  <si>
+    <t>Kompally 4</t>
+  </si>
+  <si>
+    <t>Kompally 5</t>
+  </si>
+  <si>
+    <t>MEDCHAL</t>
+  </si>
+  <si>
+    <t>SUCHITRA</t>
+  </si>
+  <si>
+    <t>TOOPRAN</t>
+  </si>
+  <si>
+    <t>MEDCHAL IPL IC</t>
+  </si>
+  <si>
+    <t>TOOPRAN 2</t>
+  </si>
+  <si>
+    <t>Ameerpet</t>
+  </si>
+  <si>
+    <t>AMEERPET</t>
+  </si>
+  <si>
+    <t>AMEERPET 2</t>
+  </si>
+  <si>
+    <t>SR NAGAR</t>
+  </si>
+  <si>
+    <t>Kukatpally</t>
+  </si>
+  <si>
+    <t>BEERAMGUDA</t>
+  </si>
+  <si>
+    <t>SANGAREDDY</t>
+  </si>
+  <si>
+    <t>SERILINGAMPALLY</t>
+  </si>
+  <si>
+    <t>CHANDA NAGAR</t>
+  </si>
+  <si>
+    <t>CHINTAL</t>
+  </si>
+  <si>
+    <t>HMT SWARNAPURI</t>
+  </si>
+  <si>
+    <t>KUKATPALLY</t>
+  </si>
+  <si>
+    <t>Kukatpally 2</t>
+  </si>
+  <si>
+    <t>NIZAMPET</t>
+  </si>
+  <si>
+    <t>SP NAGAR DS</t>
+  </si>
+  <si>
+    <t>SP NAGAR RES</t>
+  </si>
+  <si>
+    <t>VIVIN TOWERS IPL</t>
+  </si>
+  <si>
+    <t>VV NAGAR DS</t>
+  </si>
+  <si>
+    <t>VV NAGAR RES(BOYS)</t>
+  </si>
+  <si>
+    <t>KUKATPALLY CBSE</t>
+  </si>
+  <si>
+    <t>ATTAPUR</t>
+  </si>
+  <si>
+    <t>JUBILEE HILLS</t>
+  </si>
+  <si>
+    <t>MAILARDEVPALLY</t>
+  </si>
+  <si>
+    <t>Manikonda</t>
+  </si>
+  <si>
+    <t>Shamshabad</t>
+  </si>
+  <si>
+    <t>Sun City</t>
+  </si>
+  <si>
+    <t>TOLICHOWKI 1</t>
+  </si>
+  <si>
+    <t>KISMATPUR</t>
+  </si>
+  <si>
+    <t>AMEERPET CBSE</t>
+  </si>
+  <si>
+    <t>GACHIBOWLI</t>
+  </si>
+  <si>
+    <t>MIYAPUR FUTURE PATHWAYS</t>
+  </si>
+  <si>
+    <t>NALLAGANDLA</t>
+  </si>
+  <si>
+    <t>G.V.Ramana Rao</t>
+  </si>
+  <si>
+    <t>K.Srinivasa Rao</t>
+  </si>
+  <si>
+    <t>P.Shiva Rama Krishna</t>
+  </si>
+  <si>
+    <t>Padmaja</t>
+  </si>
+  <si>
+    <t>Y.Anitha</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> M.Hari Krishna</t>
   </si>
 </sst>
 </file>
@@ -468,7 +396,88 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -863,19 +872,19 @@
     </row>
     <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2" s="5">
         <v>792400</v>
@@ -907,19 +916,19 @@
     </row>
     <row r="3" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3" s="8">
         <v>1414909</v>
@@ -951,19 +960,19 @@
     </row>
     <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4" s="5">
         <v>1029699</v>
@@ -995,19 +1004,19 @@
     </row>
     <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F5" s="8">
         <v>1969433</v>
@@ -1039,19 +1048,19 @@
     </row>
     <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F6" s="5">
         <v>490250</v>
@@ -1083,19 +1092,19 @@
     </row>
     <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F7" s="8">
         <v>588958</v>
@@ -1127,19 +1136,19 @@
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F8" s="5">
         <v>331900</v>
@@ -1171,19 +1180,19 @@
     </row>
     <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F9" s="8">
         <v>186250</v>
@@ -1215,19 +1224,19 @@
     </row>
     <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -1259,19 +1268,19 @@
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -1303,19 +1312,19 @@
     </row>
     <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -1347,19 +1356,19 @@
     </row>
     <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F13" s="8">
         <v>63350</v>
@@ -1391,19 +1400,19 @@
     </row>
     <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F14" s="5">
         <v>6750</v>
@@ -1435,19 +1444,19 @@
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -1479,19 +1488,19 @@
     </row>
     <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F16" s="5">
         <v>15000</v>
@@ -1523,19 +1532,19 @@
     </row>
     <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F17" s="8">
         <v>74450</v>
@@ -1567,19 +1576,19 @@
     </row>
     <row r="18" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F18" s="5">
         <v>161820</v>
@@ -1611,19 +1620,19 @@
     </row>
     <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F19" s="8">
         <v>166265</v>
@@ -1655,19 +1664,19 @@
     </row>
     <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F20" s="5">
         <v>658210</v>
@@ -1699,19 +1708,19 @@
     </row>
     <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F21" s="8">
         <v>183700</v>
@@ -1743,19 +1752,19 @@
     </row>
     <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F22" s="5">
         <v>260500</v>
@@ -1787,19 +1796,19 @@
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F23" s="8">
         <v>15500</v>
@@ -1831,19 +1840,19 @@
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="E24" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F24" s="5">
         <v>0</v>
@@ -1875,19 +1884,19 @@
     </row>
     <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F25" s="8">
         <v>82500</v>
@@ -1919,19 +1928,19 @@
     </row>
     <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F26" s="5">
         <v>48000</v>
@@ -1963,19 +1972,19 @@
     </row>
     <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F27" s="8">
         <v>144100</v>
@@ -2007,19 +2016,19 @@
     </row>
     <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F28" s="5">
         <v>233080</v>
@@ -2051,19 +2060,19 @@
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F29" s="8">
         <v>0</v>
@@ -2095,19 +2104,19 @@
     </row>
     <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F30" s="5">
         <v>55500</v>
@@ -2139,19 +2148,19 @@
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F31" s="8">
         <v>302340</v>
@@ -2183,19 +2192,19 @@
     </row>
     <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F32" s="5">
         <v>0</v>
@@ -2227,19 +2236,19 @@
     </row>
     <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -2271,19 +2280,19 @@
     </row>
     <row r="34" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="E34" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F34" s="5">
         <v>60400</v>
@@ -2315,19 +2324,19 @@
     </row>
     <row r="35" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -2359,19 +2368,19 @@
     </row>
     <row r="36" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F36" s="5">
         <v>183500</v>
@@ -2403,19 +2412,19 @@
     </row>
     <row r="37" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F37" s="8">
         <v>580325</v>
@@ -2447,19 +2456,19 @@
     </row>
     <row r="38" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>65</v>
-      </c>
       <c r="E38" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F38" s="5">
         <v>262439</v>
@@ -2491,19 +2500,19 @@
     </row>
     <row r="39" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F39" s="8">
         <v>159600</v>
@@ -2535,19 +2544,19 @@
     </row>
     <row r="40" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F40" s="5">
         <v>113500</v>
@@ -2579,19 +2588,19 @@
     </row>
     <row r="41" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="7" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F41" s="8">
         <v>152060</v>
@@ -2622,842 +2631,321 @@
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" s="5">
-        <v>792400</v>
-      </c>
-      <c r="G42" s="5">
-        <v>41</v>
-      </c>
-      <c r="H42" s="5">
-        <v>196000</v>
-      </c>
-      <c r="I42" s="5">
-        <v>8</v>
-      </c>
-      <c r="J42" s="5">
-        <v>2</v>
-      </c>
-      <c r="K42" s="5">
-        <v>171</v>
-      </c>
-      <c r="L42" s="5">
-        <v>9612250</v>
-      </c>
-      <c r="M42" s="5">
-        <v>30</v>
-      </c>
-      <c r="N42" s="5">
-        <v>13</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
     </row>
     <row r="43" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F43" s="8">
-        <v>1414909</v>
-      </c>
-      <c r="G43" s="8">
-        <v>60</v>
-      </c>
-      <c r="H43" s="8">
-        <v>192000</v>
-      </c>
-      <c r="I43" s="8">
-        <v>8</v>
-      </c>
-      <c r="J43" s="8">
-        <v>0</v>
-      </c>
-      <c r="K43" s="8">
-        <v>85</v>
-      </c>
-      <c r="L43" s="8">
-        <v>7450990</v>
-      </c>
-      <c r="M43" s="8">
-        <v>16</v>
-      </c>
-      <c r="N43" s="8">
-        <v>7</v>
-      </c>
+      <c r="A43" s="7"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
     </row>
     <row r="44" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" s="5">
-        <v>1029699</v>
-      </c>
-      <c r="G44" s="5">
-        <v>79</v>
-      </c>
-      <c r="H44" s="5">
-        <v>104999</v>
-      </c>
-      <c r="I44" s="5">
-        <v>10</v>
-      </c>
-      <c r="J44" s="5">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5">
-        <v>121</v>
-      </c>
-      <c r="L44" s="5">
-        <v>8104730</v>
-      </c>
-      <c r="M44" s="5">
-        <v>42</v>
-      </c>
-      <c r="N44" s="5">
-        <v>15</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
     </row>
     <row r="45" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" s="8">
-        <v>1969433</v>
-      </c>
-      <c r="G45" s="8">
-        <v>84</v>
-      </c>
-      <c r="H45" s="8">
-        <v>392399</v>
-      </c>
-      <c r="I45" s="8">
-        <v>20</v>
-      </c>
-      <c r="J45" s="8">
-        <v>0</v>
-      </c>
-      <c r="K45" s="8">
-        <v>367</v>
-      </c>
-      <c r="L45" s="8">
-        <v>23083074</v>
-      </c>
-      <c r="M45" s="8">
-        <v>28</v>
-      </c>
-      <c r="N45" s="8">
-        <v>47</v>
-      </c>
+      <c r="A45" s="7"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
     </row>
     <row r="46" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="10">
-        <v>490250</v>
-      </c>
-      <c r="G46" s="10">
-        <v>25</v>
-      </c>
-      <c r="H46" s="10">
-        <v>276830</v>
-      </c>
-      <c r="I46" s="10">
-        <v>8</v>
-      </c>
-      <c r="J46" s="10">
-        <v>0</v>
-      </c>
-      <c r="K46" s="10">
-        <v>56</v>
-      </c>
-      <c r="L46" s="10">
-        <v>4731889</v>
-      </c>
-      <c r="M46" s="10">
-        <v>30</v>
-      </c>
-      <c r="N46" s="10">
-        <v>8</v>
-      </c>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
     </row>
     <row r="47" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" s="8">
-        <v>588958</v>
-      </c>
-      <c r="G47" s="8">
-        <v>37</v>
-      </c>
-      <c r="H47" s="8">
-        <v>296358</v>
-      </c>
-      <c r="I47" s="8">
-        <v>18</v>
-      </c>
-      <c r="J47" s="8">
-        <v>0</v>
-      </c>
-      <c r="K47" s="8">
-        <v>162</v>
-      </c>
-      <c r="L47" s="8">
-        <v>7456630</v>
-      </c>
-      <c r="M47" s="8">
-        <v>32</v>
-      </c>
-      <c r="N47" s="8">
-        <v>28</v>
-      </c>
+      <c r="A47" s="7"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
     </row>
     <row r="48" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F48" s="5">
-        <v>331900</v>
-      </c>
-      <c r="G48" s="5">
-        <v>21</v>
-      </c>
-      <c r="H48" s="5">
-        <v>59000</v>
-      </c>
-      <c r="I48" s="5">
-        <v>5</v>
-      </c>
-      <c r="J48" s="5">
-        <v>0</v>
-      </c>
-      <c r="K48" s="5">
-        <v>180</v>
-      </c>
-      <c r="L48" s="5">
-        <v>10830996</v>
-      </c>
-      <c r="M48" s="5">
-        <v>12</v>
-      </c>
-      <c r="N48" s="5">
-        <v>12</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
     </row>
     <row r="49" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" s="8">
-        <v>186250</v>
-      </c>
-      <c r="G49" s="8">
-        <v>11</v>
-      </c>
-      <c r="H49" s="8">
-        <v>18600</v>
-      </c>
-      <c r="I49" s="8">
-        <v>1</v>
-      </c>
-      <c r="J49" s="8">
-        <v>0</v>
-      </c>
-      <c r="K49" s="8">
-        <v>106</v>
-      </c>
-      <c r="L49" s="8">
-        <v>5645325</v>
-      </c>
-      <c r="M49" s="8">
-        <v>7</v>
-      </c>
-      <c r="N49" s="8">
-        <v>2</v>
-      </c>
+      <c r="A49" s="7"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
     </row>
     <row r="50" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F50" s="5">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5">
-        <v>0</v>
-      </c>
-      <c r="H50" s="5">
-        <v>0</v>
-      </c>
-      <c r="I50" s="5">
-        <v>0</v>
-      </c>
-      <c r="J50" s="5">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5">
-        <v>11</v>
-      </c>
-      <c r="L50" s="5">
-        <v>1018000</v>
-      </c>
-      <c r="M50" s="5">
-        <v>13</v>
-      </c>
-      <c r="N50" s="5">
-        <v>2</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
     </row>
     <row r="51" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" s="8">
-        <v>0</v>
-      </c>
-      <c r="G51" s="8">
-        <v>0</v>
-      </c>
-      <c r="H51" s="8">
-        <v>0</v>
-      </c>
-      <c r="I51" s="8">
-        <v>0</v>
-      </c>
-      <c r="J51" s="8">
-        <v>0</v>
-      </c>
-      <c r="K51" s="8">
-        <v>98</v>
-      </c>
-      <c r="L51" s="8">
-        <v>4704570</v>
-      </c>
-      <c r="M51" s="8">
-        <v>1</v>
-      </c>
-      <c r="N51" s="8">
-        <v>0</v>
-      </c>
+      <c r="A51" s="7"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
     </row>
     <row r="52" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" s="5">
-        <v>0</v>
-      </c>
-      <c r="G52" s="5">
-        <v>0</v>
-      </c>
-      <c r="H52" s="5">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5">
-        <v>0</v>
-      </c>
-      <c r="J52" s="5">
-        <v>0</v>
-      </c>
-      <c r="K52" s="5">
-        <v>6</v>
-      </c>
-      <c r="L52" s="5">
-        <v>580000</v>
-      </c>
-      <c r="M52" s="5">
-        <v>3</v>
-      </c>
-      <c r="N52" s="5">
-        <v>0</v>
-      </c>
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
     </row>
     <row r="53" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="8">
-        <v>63350</v>
-      </c>
-      <c r="G53" s="8">
-        <v>6</v>
-      </c>
-      <c r="H53" s="8">
-        <v>0</v>
-      </c>
-      <c r="I53" s="8">
-        <v>0</v>
-      </c>
-      <c r="J53" s="8">
-        <v>0</v>
-      </c>
-      <c r="K53" s="8">
-        <v>130</v>
-      </c>
-      <c r="L53" s="8">
-        <v>7259835</v>
-      </c>
-      <c r="M53" s="8">
-        <v>18</v>
-      </c>
-      <c r="N53" s="8">
-        <v>7</v>
-      </c>
+      <c r="A53" s="7"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
     </row>
     <row r="54" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F54" s="5">
-        <v>6750</v>
-      </c>
-      <c r="G54" s="5">
-        <v>1</v>
-      </c>
-      <c r="H54" s="5">
-        <v>0</v>
-      </c>
-      <c r="I54" s="5">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5">
-        <v>66</v>
-      </c>
-      <c r="L54" s="5">
-        <v>6741852</v>
-      </c>
-      <c r="M54" s="5">
-        <v>15</v>
-      </c>
-      <c r="N54" s="5">
-        <v>7</v>
-      </c>
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
     </row>
     <row r="55" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F55" s="8">
-        <v>0</v>
-      </c>
-      <c r="G55" s="8">
-        <v>0</v>
-      </c>
-      <c r="H55" s="8">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8">
-        <v>0</v>
-      </c>
-      <c r="K55" s="8">
-        <v>10</v>
-      </c>
-      <c r="L55" s="8">
-        <v>527600</v>
-      </c>
-      <c r="M55" s="8">
-        <v>4</v>
-      </c>
-      <c r="N55" s="8">
-        <v>0</v>
-      </c>
+      <c r="A55" s="7"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
     </row>
     <row r="56" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="5">
-        <v>15000</v>
-      </c>
-      <c r="G56" s="5">
-        <v>1</v>
-      </c>
-      <c r="H56" s="5">
-        <v>0</v>
-      </c>
-      <c r="I56" s="5">
-        <v>0</v>
-      </c>
-      <c r="J56" s="5">
-        <v>0</v>
-      </c>
-      <c r="K56" s="5">
-        <v>56</v>
-      </c>
-      <c r="L56" s="5">
-        <v>3531100</v>
-      </c>
-      <c r="M56" s="5">
-        <v>0</v>
-      </c>
-      <c r="N56" s="5">
-        <v>0</v>
-      </c>
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
     </row>
     <row r="57" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="8">
-        <v>74450</v>
-      </c>
-      <c r="G57" s="8">
-        <v>5</v>
-      </c>
-      <c r="H57" s="8">
-        <v>0</v>
-      </c>
-      <c r="I57" s="8">
-        <v>0</v>
-      </c>
-      <c r="J57" s="8">
-        <v>0</v>
-      </c>
-      <c r="K57" s="8">
-        <v>56</v>
-      </c>
-      <c r="L57" s="8">
-        <v>3640925</v>
-      </c>
-      <c r="M57" s="8">
-        <v>49</v>
-      </c>
-      <c r="N57" s="8">
-        <v>12</v>
-      </c>
+      <c r="A57" s="7"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
     </row>
     <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F58" s="5">
-        <v>161820</v>
-      </c>
-      <c r="G58" s="5">
-        <v>13</v>
-      </c>
-      <c r="H58" s="5">
-        <v>29225</v>
-      </c>
-      <c r="I58" s="5">
-        <v>1</v>
-      </c>
-      <c r="J58" s="5">
-        <v>0</v>
-      </c>
-      <c r="K58" s="5">
-        <v>95</v>
-      </c>
-      <c r="L58" s="5">
-        <v>4357000</v>
-      </c>
-      <c r="M58" s="5">
-        <v>16</v>
-      </c>
-      <c r="N58" s="5">
-        <v>15</v>
-      </c>
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
     </row>
     <row r="59" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="8">
-        <v>166265</v>
-      </c>
-      <c r="G59" s="8">
-        <v>10</v>
-      </c>
-      <c r="H59" s="8">
-        <v>54450</v>
-      </c>
-      <c r="I59" s="8">
-        <v>2</v>
-      </c>
-      <c r="J59" s="8">
-        <v>0</v>
-      </c>
-      <c r="K59" s="8">
-        <v>66</v>
-      </c>
-      <c r="L59" s="8">
-        <v>4887125</v>
-      </c>
-      <c r="M59" s="8">
-        <v>37</v>
-      </c>
-      <c r="N59" s="8">
-        <v>16</v>
-      </c>
+      <c r="A59" s="7"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
     </row>
     <row r="60" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F60" s="5">
-        <v>658210</v>
-      </c>
-      <c r="G60" s="5">
-        <v>15</v>
-      </c>
-      <c r="H60" s="5">
-        <v>45910</v>
-      </c>
-      <c r="I60" s="5">
-        <v>1</v>
-      </c>
-      <c r="J60" s="5">
-        <v>0</v>
-      </c>
-      <c r="K60" s="5">
-        <v>56</v>
-      </c>
-      <c r="L60" s="5">
-        <v>4274060</v>
-      </c>
-      <c r="M60" s="5">
-        <v>4</v>
-      </c>
-      <c r="N60" s="5">
-        <v>10</v>
-      </c>
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D41">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>